--- a/tame_output/ON/bt/strategyON_20231224.xlsx
+++ b/tame_output/ON/bt/strategyON_20231224.xlsx
@@ -1012,7 +1012,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>591.5%</t>
+          <t>591.3%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -43399,10 +43399,10 @@
         <v>3.134450814492048</v>
       </c>
       <c r="D1821" t="n">
-        <v>0.2604903832097689</v>
+        <v>0.2600489929898902</v>
       </c>
       <c r="E1821" t="n">
-        <v>3.238290543462209</v>
+        <v>3.238113987374257</v>
       </c>
       <c r="F1821" t="n">
         <v>1.820317739666588</v>

--- a/tame_output/ON/bt/strategyON_20231224.xlsx
+++ b/tame_output/ON/bt/strategyON_20231224.xlsx
@@ -595,17 +595,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>48.7%</t>
+          <t>50.6%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>67.1%</t>
+          <t>66.9%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -628,7 +628,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -671,12 +671,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>19.0%</t>
+          <t>18.4%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.6%</t>
+          <t>-11.9%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -736,7 +736,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>88.7%</t>
+          <t>94.0%</t>
         </is>
       </c>
     </row>
@@ -839,7 +839,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>67.0%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-24.0%</t>
+          <t>-24.1%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>75.7%</t>
+          <t>75.9%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.5%</t>
+          <t>52.4%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -939,7 +939,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>67.0%</t>
+          <t>67.4%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,12 +977,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>18.3%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-24.6%</t>
+          <t>-24.8%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-10.7%</t>
+          <t>-10.3%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>61.9%</t>
+          <t>62.1%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1012,12 +1012,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>591.3%</t>
+          <t>518.5%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-160.1%</t>
+          <t>-159.9%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1092,12 +1092,12 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>38.1%</t>
+          <t>38.2%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>87.5%</t>
+          <t>87.7%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1130,12 +1130,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>11.6%</t>
+          <t>11.7%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-17.1%</t>
+          <t>-17.3%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-18.8%</t>
+          <t>-18.9%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>40.4%</t>
+          <t>40.3%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>40.3%</t>
+          <t>40.6%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>109.9%</t>
+          <t>109.8%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -42525,10 +42525,10 @@
         <v>3.0856881010767</v>
       </c>
       <c r="D1783" t="n">
-        <v>-3.420891470204585</v>
+        <v>-3.477006956979778</v>
       </c>
       <c r="E1783" t="n">
-        <v>1.716975088681119</v>
+        <v>1.694528893971041</v>
       </c>
       <c r="F1783" t="n">
         <v>0.1940033476978162</v>
@@ -42548,10 +42548,10 @@
         <v>3.089704189836242</v>
       </c>
       <c r="D1784" t="n">
-        <v>-3.432696820523217</v>
+        <v>-3.488812307298411</v>
       </c>
       <c r="E1784" t="n">
-        <v>1.716269037313208</v>
+        <v>1.693822842603131</v>
       </c>
       <c r="F1784" t="n">
         <v>0.1821979973791836</v>
@@ -42571,10 +42571,10 @@
         <v>3.095651647446132</v>
       </c>
       <c r="D1785" t="n">
-        <v>-3.423965009744551</v>
+        <v>-3.480080496519744</v>
       </c>
       <c r="E1785" t="n">
-        <v>1.725709219234564</v>
+        <v>1.703263024524487</v>
       </c>
       <c r="F1785" t="n">
         <v>0.1909298081578498</v>
@@ -42594,10 +42594,10 @@
         <v>3.090962466394117</v>
       </c>
       <c r="D1786" t="n">
-        <v>-3.417628123100099</v>
+        <v>-3.473743609875292</v>
       </c>
       <c r="E1786" t="n">
-        <v>1.723554792840331</v>
+        <v>1.701108598130253</v>
       </c>
       <c r="F1786" t="n">
         <v>0.1909298081578498</v>
@@ -42617,10 +42617,10 @@
         <v>3.100925124196311</v>
       </c>
       <c r="D1787" t="n">
-        <v>-3.41509367537273</v>
+        <v>-3.471209162147924</v>
       </c>
       <c r="E1787" t="n">
-        <v>1.734531229733472</v>
+        <v>1.712085035023394</v>
       </c>
       <c r="F1787" t="n">
         <v>0.1909298081578498</v>
@@ -42640,10 +42640,10 @@
         <v>3.09333980438922</v>
       </c>
       <c r="D1788" t="n">
-        <v>-3.415169574353335</v>
+        <v>-3.471285061128528</v>
       </c>
       <c r="E1788" t="n">
-        <v>1.72691555033414</v>
+        <v>1.704469355624062</v>
       </c>
       <c r="F1788" t="n">
         <v>0.1916930688471767</v>
@@ -42663,10 +42663,10 @@
         <v>3.071104380179594</v>
       </c>
       <c r="D1789" t="n">
-        <v>-3.425671763912681</v>
+        <v>-3.481787250687875</v>
       </c>
       <c r="E1789" t="n">
-        <v>1.700479250300774</v>
+        <v>1.678033055590697</v>
       </c>
       <c r="F1789" t="n">
         <v>0.1811908792878301</v>
@@ -42686,10 +42686,10 @@
         <v>3.071805220025715</v>
       </c>
       <c r="D1790" t="n">
-        <v>-3.427505026591798</v>
+        <v>-3.483620513366991</v>
       </c>
       <c r="E1790" t="n">
-        <v>1.700446785075249</v>
+        <v>1.678000590365172</v>
       </c>
       <c r="F1790" t="n">
         <v>0.1811908792878301</v>
@@ -42709,10 +42709,10 @@
         <v>3.072322299854575</v>
       </c>
       <c r="D1791" t="n">
-        <v>-3.432514141653382</v>
+        <v>-3.488629628428575</v>
       </c>
       <c r="E1791" t="n">
-        <v>1.698960218879475</v>
+        <v>1.676514024169398</v>
       </c>
       <c r="F1791" t="n">
         <v>0.1801963017292953</v>
@@ -42732,10 +42732,10 @@
         <v>3.07155002509494</v>
       </c>
       <c r="D1792" t="n">
-        <v>-3.436219698290196</v>
+        <v>-3.49233518506539</v>
       </c>
       <c r="E1792" t="n">
-        <v>1.696705721465115</v>
+        <v>1.674259526755037</v>
       </c>
       <c r="F1792" t="n">
         <v>0.1783266264716604</v>
@@ -42755,10 +42755,10 @@
         <v>3.071969877157259</v>
       </c>
       <c r="D1793" t="n">
-        <v>-3.434987372932831</v>
+        <v>-3.491102859708024</v>
       </c>
       <c r="E1793" t="n">
-        <v>1.69761850367038</v>
+        <v>1.675172308960303</v>
       </c>
       <c r="F1793" t="n">
         <v>0.178957002843698</v>
@@ -42778,10 +42778,10 @@
         <v>3.076099785321473</v>
       </c>
       <c r="D1794" t="n">
-        <v>-3.424659375916979</v>
+        <v>-3.480774862692172</v>
       </c>
       <c r="E1794" t="n">
-        <v>1.705879610640935</v>
+        <v>1.683433415930857</v>
       </c>
       <c r="F1794" t="n">
         <v>0.1892849998595502</v>
@@ -42801,10 +42801,10 @@
         <v>3.082620445523309</v>
       </c>
       <c r="D1795" t="n">
-        <v>-3.424543040769423</v>
+        <v>-3.480658527544616</v>
       </c>
       <c r="E1795" t="n">
-        <v>1.712446804901793</v>
+        <v>1.690000610191716</v>
       </c>
       <c r="F1795" t="n">
         <v>0.1894013350071059</v>
@@ -42824,10 +42824,10 @@
         <v>3.079594415968698</v>
       </c>
       <c r="D1796" t="n">
-        <v>-3.42638845034629</v>
+        <v>-3.482503937121484</v>
       </c>
       <c r="E1796" t="n">
-        <v>1.708682611516435</v>
+        <v>1.686236416806357</v>
       </c>
       <c r="F1796" t="n">
         <v>0.1894013350071059</v>
@@ -42847,10 +42847,10 @@
         <v>3.079532703829831</v>
       </c>
       <c r="D1797" t="n">
-        <v>-3.424890017821191</v>
+        <v>-3.481005504596385</v>
       </c>
       <c r="E1797" t="n">
-        <v>1.709220272387608</v>
+        <v>1.68677407767753</v>
       </c>
       <c r="F1797" t="n">
         <v>0.1908997675322048</v>
@@ -42870,10 +42870,10 @@
         <v>3.080810681773143</v>
       </c>
       <c r="D1798" t="n">
-        <v>-3.432954270013925</v>
+        <v>-3.489069756789119</v>
       </c>
       <c r="E1798" t="n">
-        <v>1.707272549453826</v>
+        <v>1.684826354743749</v>
       </c>
       <c r="F1798" t="n">
         <v>0.182835515339471</v>
@@ -42893,10 +42893,10 @@
         <v>3.080810681773143</v>
       </c>
       <c r="D1799" t="n">
-        <v>-3.434284237475137</v>
+        <v>-3.490399724250331</v>
       </c>
       <c r="E1799" t="n">
-        <v>1.706740562469341</v>
+        <v>1.684294367759264</v>
       </c>
       <c r="F1799" t="n">
         <v>0.182835515339471</v>
@@ -42916,10 +42916,10 @@
         <v>3.083027154880305</v>
       </c>
       <c r="D1800" t="n">
-        <v>-3.206419554741626</v>
+        <v>-3.26253504151682</v>
       </c>
       <c r="E1800" t="n">
-        <v>1.800102908669908</v>
+        <v>1.77765671395983</v>
       </c>
       <c r="F1800" t="n">
         <v>0.182835515339471</v>
@@ -42939,10 +42939,10 @@
         <v>3.090561751225397</v>
       </c>
       <c r="D1801" t="n">
-        <v>-2.958317990874409</v>
+        <v>-3.014433477649603</v>
       </c>
       <c r="E1801" t="n">
-        <v>1.906878130561887</v>
+        <v>1.884431935851809</v>
       </c>
       <c r="F1801" t="n">
         <v>0.182835515339471</v>
@@ -42962,10 +42962,10 @@
         <v>3.091984762198855</v>
       </c>
       <c r="D1802" t="n">
-        <v>-2.661479591481079</v>
+        <v>-2.717595078256273</v>
       </c>
       <c r="E1802" t="n">
-        <v>2.027036501292676</v>
+        <v>2.004590306582599</v>
       </c>
       <c r="F1802" t="n">
         <v>0.2976900038205986</v>
@@ -42985,10 +42985,10 @@
         <v>3.093661836664541</v>
       </c>
       <c r="D1803" t="n">
-        <v>-2.357840034655643</v>
+        <v>-2.413955521430836</v>
       </c>
       <c r="E1803" t="n">
-        <v>2.150169398488537</v>
+        <v>2.12772320377846</v>
       </c>
       <c r="F1803" t="n">
         <v>0.2976900038205986</v>
@@ -43008,10 +43008,10 @@
         <v>3.089601258113999</v>
       </c>
       <c r="D1804" t="n">
-        <v>-2.068819428214934</v>
+        <v>-2.124934914990128</v>
       </c>
       <c r="E1804" t="n">
-        <v>2.261717062514278</v>
+        <v>2.239270867804201</v>
       </c>
       <c r="F1804" t="n">
         <v>0.2976900038205986</v>
@@ -43031,10 +43031,10 @@
         <v>3.094821397458016</v>
       </c>
       <c r="D1805" t="n">
-        <v>-1.784099500951037</v>
+        <v>-1.840214987726231</v>
       </c>
       <c r="E1805" t="n">
-        <v>2.380825172763855</v>
+        <v>2.358378978053777</v>
       </c>
       <c r="F1805" t="n">
         <v>0.5824099310844958</v>
@@ -43054,10 +43054,10 @@
         <v>3.100133560631823</v>
       </c>
       <c r="D1806" t="n">
-        <v>-1.500337831459497</v>
+        <v>-1.55645331823469</v>
       </c>
       <c r="E1806" t="n">
-        <v>2.499642003734278</v>
+        <v>2.4771958090242</v>
       </c>
       <c r="F1806" t="n">
         <v>0.5824099310844958</v>
@@ -43077,10 +43077,10 @@
         <v>3.093376148078457</v>
       </c>
       <c r="D1807" t="n">
-        <v>-1.238689437066856</v>
+        <v>-1.29480492384205</v>
       </c>
       <c r="E1807" t="n">
-        <v>2.597543948937968</v>
+        <v>2.57509775422789</v>
       </c>
       <c r="F1807" t="n">
         <v>0.8440583254771364</v>
@@ -43100,10 +43100,10 @@
         <v>3.090839823094569</v>
       </c>
       <c r="D1808" t="n">
-        <v>-0.9245229989275235</v>
+        <v>-0.9806384857027172</v>
       </c>
       <c r="E1808" t="n">
-        <v>2.720674199209813</v>
+        <v>2.698228004499736</v>
       </c>
       <c r="F1808" t="n">
         <v>1.158224763616469</v>
@@ -43123,10 +43123,10 @@
         <v>3.109254206721308</v>
       </c>
       <c r="D1809" t="n">
-        <v>-0.8020112948217512</v>
+        <v>-0.8581267815969448</v>
       </c>
       <c r="E1809" t="n">
-        <v>2.788093264478861</v>
+        <v>2.765647069768784</v>
       </c>
       <c r="F1809" t="n">
         <v>1.280736467722241</v>
@@ -43146,10 +43146,10 @@
         <v>3.119070330776787</v>
       </c>
       <c r="D1810" t="n">
-        <v>-0.6406227608950228</v>
+        <v>-0.6967382476702164</v>
       </c>
       <c r="E1810" t="n">
-        <v>2.862464802105031</v>
+        <v>2.840018607394954</v>
       </c>
       <c r="F1810" t="n">
         <v>1.44212500164897</v>
@@ -43169,10 +43169,10 @@
         <v>3.132597942828719</v>
       </c>
       <c r="D1811" t="n">
-        <v>-0.4608765697465166</v>
+        <v>-0.5169920565217102</v>
       </c>
       <c r="E1811" t="n">
-        <v>2.947890890616365</v>
+        <v>2.925444695906288</v>
       </c>
       <c r="F1811" t="n">
         <v>1.44212500164897</v>
@@ -43192,10 +43192,10 @@
         <v>3.139185323079984</v>
       </c>
       <c r="D1812" t="n">
-        <v>-0.3020756432752937</v>
+        <v>-0.3581911300504873</v>
       </c>
       <c r="E1812" t="n">
-        <v>3.01799864145612</v>
+        <v>2.995552446746043</v>
       </c>
       <c r="F1812" t="n">
         <v>1.44212500164897</v>
@@ -43215,10 +43215,10 @@
         <v>3.128096071514691</v>
       </c>
       <c r="D1813" t="n">
-        <v>-0.2092871849699168</v>
+        <v>-0.2654026717451105</v>
       </c>
       <c r="E1813" t="n">
-        <v>3.044024773212977</v>
+        <v>3.0215785785029</v>
       </c>
       <c r="F1813" t="n">
         <v>1.534913459954347</v>
@@ -43238,10 +43238,10 @@
         <v>3.123696569025415</v>
       </c>
       <c r="D1814" t="n">
-        <v>-0.1152666895990749</v>
+        <v>-0.1713821763742686</v>
       </c>
       <c r="E1814" t="n">
-        <v>3.077233468872038</v>
+        <v>3.054787274161961</v>
       </c>
       <c r="F1814" t="n">
         <v>1.54475590044733</v>
@@ -43261,10 +43261,10 @@
         <v>3.109676345532145</v>
       </c>
       <c r="D1815" t="n">
-        <v>-0.02516372169255188</v>
+        <v>-0.0812792084677455</v>
       </c>
       <c r="E1815" t="n">
-        <v>3.099254432541378</v>
+        <v>3.0768082378313</v>
       </c>
       <c r="F1815" t="n">
         <v>1.547814094735116</v>
@@ -43284,10 +43284,10 @@
         <v>3.127125924287274</v>
       </c>
       <c r="D1816" t="n">
-        <v>0.01896544902902331</v>
+        <v>-0.03715003774617032</v>
       </c>
       <c r="E1816" t="n">
-        <v>3.134355679585136</v>
+        <v>3.111909484875059</v>
       </c>
       <c r="F1816" t="n">
         <v>1.631833267722386</v>
@@ -43307,10 +43307,10 @@
         <v>3.126153974671351</v>
       </c>
       <c r="D1817" t="n">
-        <v>0.02873549320671809</v>
+        <v>-0.02737999356847554</v>
       </c>
       <c r="E1817" t="n">
-        <v>3.137291747640291</v>
+        <v>3.114845552930214</v>
       </c>
       <c r="F1817" t="n">
         <v>1.711192158777452</v>
@@ -43330,10 +43330,10 @@
         <v>3.115456695754193</v>
       </c>
       <c r="D1818" t="n">
-        <v>0.06537381597469277</v>
+        <v>0.009258329199499149</v>
       </c>
       <c r="E1818" t="n">
-        <v>3.141249797830324</v>
+        <v>3.118803603120246</v>
       </c>
       <c r="F1818" t="n">
         <v>1.711192158777452</v>
@@ -43353,10 +43353,10 @@
         <v>3.125373651216407</v>
       </c>
       <c r="D1819" t="n">
-        <v>0.1140194944444261</v>
+        <v>0.05790400766923243</v>
       </c>
       <c r="E1819" t="n">
-        <v>3.170625024680431</v>
+        <v>3.148178829970353</v>
       </c>
       <c r="F1819" t="n">
         <v>1.759837837247185</v>
@@ -43376,10 +43376,10 @@
         <v>3.132226628875955</v>
       </c>
       <c r="D1820" t="n">
-        <v>0.1744993968638284</v>
+        <v>0.1183839100886347</v>
       </c>
       <c r="E1820" t="n">
-        <v>3.201669963307739</v>
+        <v>3.179223768597662</v>
       </c>
       <c r="F1820" t="n">
         <v>1.820317739666588</v>
@@ -43393,16 +43393,16 @@
         <v>45283</v>
       </c>
       <c r="B1821" t="n">
-        <v>3.122585942670183</v>
+        <v>3.175615512574396</v>
       </c>
       <c r="C1821" t="n">
         <v>3.134450814492048</v>
       </c>
       <c r="D1821" t="n">
-        <v>0.2600489929898902</v>
+        <v>0.2602349115699303</v>
       </c>
       <c r="E1821" t="n">
-        <v>3.238113987374257</v>
+        <v>3.238188354806273</v>
       </c>
       <c r="F1821" t="n">
         <v>1.820317739666588</v>

--- a/tame_output/ON/bt/strategyON_20231224.xlsx
+++ b/tame_output/ON/bt/strategyON_20231224.xlsx
@@ -901,17 +901,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-24.1%</t>
+          <t>-24.9%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>75.9%</t>
+          <t>75.7%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -939,7 +939,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>67.4%</t>
+          <t>67.1%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>18.3%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-10.3%</t>
+          <t>-11.5%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>62.1%</t>
+          <t>61.9%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>518.5%</t>
+          <t>510.8%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>-116.4%</t>
+          <t>-122.3%</t>
         </is>
       </c>
     </row>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>75.3%</t>
+          <t>74.5%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1092,7 +1092,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>38.2%</t>
+          <t>38.1%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>11.7%</t>
+          <t>11.6%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>72.1%</t>
+          <t>71.1%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-18.9%</t>
+          <t>-18.8%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>-18.6%</t>
+          <t>-21.0%</t>
         </is>
       </c>
     </row>
@@ -43399,10 +43399,10 @@
         <v>3.134450814492048</v>
       </c>
       <c r="D1821" t="n">
-        <v>0.2602349115699303</v>
+        <v>0.2009339776047517</v>
       </c>
       <c r="E1821" t="n">
-        <v>3.238188354806273</v>
+        <v>3.214467981220201</v>
       </c>
       <c r="F1821" t="n">
         <v>1.820317739666588</v>
